--- a/out/Attention-mamba2_repeat_5_000008.xlsx
+++ b/out/Attention-mamba2_repeat_5_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.043559541701984</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.043559541701984</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001324841138448101</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1521988008879794</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.443559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1524336738574807</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3681667500936273</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5846072344506439</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02623184023164717</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.268313070625972</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04600158170481162</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3340758965691389</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05588648902765958</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3998432833296647</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01478913025678568</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3734630781971859</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008215146820463731</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3750911313553671</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01726278442163607</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4014111695626413</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0067782233697855</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3976918187582795</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004826543313620532</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.400562644085574</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001896047678383832</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3995257946315671</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001073989216906629</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3997768013740985</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004060292307386027</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3995136405687409</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001876680775978301</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3994825816230085</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.604462590314975e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3994257392922556</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.59873730729961e-05</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3993916017224823</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.49368653649805e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3993865853403574</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.399382385131035</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3993794012519293</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.399373957506923</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3993679647734927</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3993625969849143</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.399362633733406</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3993627439788815</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3993628174758651</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3993630012183243</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3993645446549808</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3993660145946539</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3993672640433759</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3993686237375731</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3993664188280639</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3993660145946539</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3993651693793419</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3993657206067192</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3993653898702927</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3993650958823582</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3993651693793419</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3993647283974399</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3993646181519644</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3993645814034727</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3993647283974399</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3993642506670463</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3993652061278335</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3993651693793419</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3993648386429155</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3993652796248174</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3993646549004563</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3993644711579972</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3993640669245871</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3993632217092751</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3993631849607834</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3993633319547507</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3993632584577671</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3993633319547507</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3993633687032426</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3993632584577671</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.399363699439669</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3993635891941935</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3993635524457015</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3993634789487179</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3993634422002262</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3993632217092751</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3993631482122915</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3993630747153079</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3993631114637998</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3993630012183243</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3993631114637998</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3993634054517343</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000008.xlsx
+++ b/out/Attention-mamba2_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.3801101738204644</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.3801101738204643</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001324841138448101</v>
+        <v>-9.132992555899546e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1521988008879794</v>
+        <v>-0.1049205429382199</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.443559541701984</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.424137072939437</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1523312850018243</v>
+        <v>-0.105011872863779</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1524336738574807</v>
+        <v>-0.1051178710352895</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3681667500936273</v>
+        <v>0.3811452846635505</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5846072344506439</v>
+        <v>0.6579045111954279</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02623184023164717</v>
+        <v>0.02715652150856841</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.268313070625972</v>
+        <v>0.3304608706773415</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04600158170481162</v>
+        <v>0.04762328592578561</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3340758965691389</v>
+        <v>0.398541858258511</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05588648902765958</v>
+        <v>0.05785635634786061</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3998432833296647</v>
+        <v>0.4666273777962441</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01478913025678568</v>
+        <v>0.01531024149206785</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3734630781971859</v>
+        <v>0.4393173431964011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008215146820463731</v>
+        <v>0.008504976151364666</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3750911313553671</v>
+        <v>0.4410029752171624</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01726278442163607</v>
+        <v>0.01787144280301126</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4014111695626413</v>
+        <v>0.4682510161997534</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0067782233697855</v>
+        <v>0.00701801594739977</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3976918187582795</v>
+        <v>0.4644007024390038</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004826543313620532</v>
+        <v>0.00499558695686752</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.400562644085574</v>
+        <v>0.4673726601966561</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001896047678383832</v>
+        <v>0.001963942238326113</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3995257946315671</v>
+        <v>0.4662993395858144</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001073989216906629</v>
+        <v>0.001112524546081865</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3997768013740985</v>
+        <v>0.4665592991216036</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004060292307386027</v>
+        <v>0.0004201216615067832</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3995136405687409</v>
+        <v>0.4662872996881167</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001876680775978301</v>
+        <v>0.0001942738402583272</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3994825816230085</v>
+        <v>0.4662553498127128</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.604462590314975e-05</v>
+        <v>6.846660178621169e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3994257392922556</v>
+        <v>0.4661967401297754</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.59873730729961e-05</v>
+        <v>1.64643588246551e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3993916017224823</v>
+        <v>0.4661616096060807</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.49368653649805e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3993865853403574</v>
+        <v>0.4661565924793137</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.399382385131035</v>
+        <v>0.466152429018483</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3993794012519293</v>
+        <v>0.4661496278726053</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.399373957506923</v>
+        <v>0.466144184127599</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3993679647734927</v>
+        <v>0.4661381913941687</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3993625969849143</v>
+        <v>0.4661328236055903</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.399362633733406</v>
+        <v>0.466132860354082</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3993627439788815</v>
+        <v>0.4661329705995575</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3993628174758651</v>
+        <v>0.4661330440965411</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3993630012183243</v>
+        <v>0.4661332278390003</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3993645446549808</v>
+        <v>0.4661347712756568</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3993660145946539</v>
+        <v>0.4661362412153299</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.07536333809757492</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3993672640433759</v>
+        <v>0.4661374906640519</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.5801101738204644</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3993686237375731</v>
+        <v>0.4661388503582491</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3993664188280639</v>
+        <v>0.4661366454487399</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3993660145946539</v>
+        <v>0.4661362412153299</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.5801101738204643</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3993651693793419</v>
+        <v>0.4661353960000179</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.07536333809757502</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3993657206067192</v>
+        <v>0.4661359472273952</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3993653898702927</v>
+        <v>0.4661356164909687</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3993650958823582</v>
+        <v>0.4661353225030342</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3993651693793419</v>
+        <v>0.4661353960000179</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3993647283974399</v>
+        <v>0.4661349550181159</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3993646181519644</v>
+        <v>0.4661348447726404</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3993645814034727</v>
+        <v>0.4661348080241487</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3993647283974399</v>
+        <v>0.4661349550181159</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.424137072939437</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3993642506670463</v>
+        <v>0.4661344772877223</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.043559541701984</v>
+        <v>0.07536333809757498</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3993652061278335</v>
+        <v>0.4661354327485095</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.07536333809757498</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3993651693793419</v>
+        <v>0.4661353960000179</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3993648386429155</v>
+        <v>0.4661350652635915</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.424137072939437</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3993652796248174</v>
+        <v>0.4661355062454934</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3993646549004563</v>
+        <v>0.4661348815211323</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3993644711579972</v>
+        <v>0.4661346977786732</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3993640669245871</v>
+        <v>0.4661342935452631</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3993632217092751</v>
+        <v>0.4661334483299511</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3993631849607834</v>
+        <v>0.4661334115814594</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3993633319547507</v>
+        <v>0.4661335585754267</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3993632584577671</v>
+        <v>0.4661334850784431</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3993633319547507</v>
+        <v>0.4661335585754267</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3993633687032426</v>
+        <v>0.4661335953239186</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3993632584577671</v>
+        <v>0.4661334850784431</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.399363699439669</v>
+        <v>0.466133926060345</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3993635891941935</v>
+        <v>0.4661338158148695</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3993635524457015</v>
+        <v>0.4661337790663775</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3993634789487179</v>
+        <v>0.4661337055693939</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3993634422002262</v>
+        <v>0.4661336688209022</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3993632217092751</v>
+        <v>0.4661334483299511</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3993631482122915</v>
+        <v>0.4661333748329675</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3993630747153079</v>
+        <v>0.4661333013359839</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3993631114637998</v>
+        <v>0.4661333380844758</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3993630012183243</v>
+        <v>0.4661332278390003</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3993631114637998</v>
+        <v>0.4661333380844758</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3993634054517343</v>
+        <v>0.4661336320724103</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000008.xlsx
+++ b/out/Attention-mamba2_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.4433861970901489</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.4152671694755554</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.2963644862174988</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.08683616667985916</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1749255657196045</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1567986309528351</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1360337436199188</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.1274871528148651</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.130988597869873</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.1284980177879333</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1290612816810608</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.129293292760849</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1268866956233978</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.1268230378627777</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.1524523496627808</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.1404784023761749</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.1171558126807213</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.1220157667994499</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.1241465136408806</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1209422573447227</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.1225302740931511</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.1226400211453438</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.1224160864949226</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.1284230649471283</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.1290839016437531</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.1216214224696159</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.1242384389042854</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.1230104044079781</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.1250794231891632</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.134527176618576</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.1662095487117767</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.1497743725776672</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.1311309635639191</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.1289430260658264</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.1284578442573547</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.1330274641513824</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.1232174560427666</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.1185659244656563</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.1441553235054016</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.1473041176795959</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.1464735567569733</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.1631955802440643</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.02207104116678238</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3801101738204644</v>
+        <v>-0.16</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01772525906562805</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3801101738204643</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.132992555899546e-05</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1049205429382199</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001066118478775024</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.275363338097575</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01077421009540558</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.275363338097575</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0347556471824646</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01772760599851608</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.007703468203544617</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0006521120667457581</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.009670324623584747</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01492195948958397</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.02525581791996956</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.02645654603838921</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.02506007626652718</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.03204477950930595</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.08685635775327682</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.105011872863779</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.07577303051948547</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1051178710352895</v>
+        <v>-0.1339693976942447</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3811452846635505</v>
+        <v>0.3790050460052938</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03355105593800545</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6579045111954279</v>
+        <v>0.624768912362248</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02715652150856841</v>
+        <v>0.02700402995352339</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01808534935116768</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3304608706773415</v>
+        <v>0.2991635195881501</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04762328592578561</v>
+        <v>0.04735586769532907</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01152353733778</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.398541858258511</v>
+        <v>0.3668623968958833</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05785635634786061</v>
+        <v>0.05753209835276579</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.07669391483068466</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4666273777962441</v>
+        <v>0.4345659633063597</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01531024149206785</v>
+        <v>0.01522443470221772</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.1300777196884155</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4393173431964011</v>
+        <v>0.4074092811014506</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008504976151364666</v>
+        <v>0.008456915844595018</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02609039470553398</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4410029752171624</v>
+        <v>0.4090854019833645</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01787144280301126</v>
+        <v>0.01777128382886091</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01889290288090706</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4682510161997534</v>
+        <v>0.4361807336484985</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.00701801594739977</v>
+        <v>0.006978050517797391</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.06375201046466827</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4644007024390038</v>
+        <v>0.4323519714334582</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00499558695686752</v>
+        <v>0.004967987994704746</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.09938875585794449</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4673726601966561</v>
+        <v>0.4353075017704619</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001963942238326113</v>
+        <v>0.001953079108735347</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.09025605022907257</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4662993395858144</v>
+        <v>0.4342400753423008</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001112524546081865</v>
+        <v>0.001106358893413828</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.09857391566038132</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4665592991216036</v>
+        <v>0.4344985730323752</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004201216615067832</v>
+        <v>0.0004177729230454198</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.09509161859750748</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4662872996881167</v>
+        <v>0.4342280467035766</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001942738402583272</v>
+        <v>0.000193172879814911</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.09137557446956635</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4662553498127128</v>
+        <v>0.4341962453164514</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.846660178621169e-05</v>
+        <v>6.76592764918577e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.1059064492583275</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4661967401297754</v>
+        <v>0.4341379307629741</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.113601341843605</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4661616096060807</v>
+        <v>0.4341028002392794</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.1072305291891098</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4661565924793137</v>
+        <v>0.4340977831125125</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.1056734994053841</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.466152429018483</v>
+        <v>0.4340936196516818</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.08457488566637039</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4661496278726053</v>
+        <v>0.4340908185058041</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.1016136109828949</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.466144184127599</v>
+        <v>0.4340853747607977</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.1181949302554131</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4661381913941687</v>
+        <v>0.4340793820273673</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.1238486468791962</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4661328236055903</v>
+        <v>0.434074014238789</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.07010973989963531</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.466132860354082</v>
+        <v>0.4340740509872807</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.1206477582454681</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4661329705995575</v>
+        <v>0.4340741612327562</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.1059547960758209</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4661330440965411</v>
+        <v>0.4340742347297398</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.1115384101867676</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4661332278390003</v>
+        <v>0.434074418472199</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0800538957118988</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4661347712756568</v>
+        <v>0.4340759619088555</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0924418643116951</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4661362412153299</v>
+        <v>0.4340774318485285</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.09762071818113327</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.07536333809757492</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4661374906640519</v>
+        <v>0.4340786812972506</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.08300141245126724</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5801101738204644</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4661388503582491</v>
+        <v>0.4340800409914479</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01217237114906311</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4661366454487399</v>
+        <v>0.4340778360819386</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.06935102492570877</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4661362412153299</v>
+        <v>0.4340774318485285</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006741978228092194</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5801101738204643</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4661353960000179</v>
+        <v>0.4340765866332166</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.06228351593017578</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.07536333809757502</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4661359472273952</v>
+        <v>0.4340771378605939</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.08608069270849228</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4661356164909687</v>
+        <v>0.4340768071241675</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.08650723099708557</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4661353225030342</v>
+        <v>0.434076513136233</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.08639615029096603</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4661353960000179</v>
+        <v>0.4340765866332166</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.09167829900979996</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4661349550181159</v>
+        <v>0.4340761456513146</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.08742745220661163</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4661348447726404</v>
+        <v>0.4340760354058391</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.09026491641998291</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4661348080241487</v>
+        <v>0.4340759986573474</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.1050290614366531</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4661349550181159</v>
+        <v>0.4340761456513146</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.04824085161089897</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.275363338097575</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4661344772877223</v>
+        <v>0.434075667920921</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.0100543275475502</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.07536333809757498</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4661354327485095</v>
+        <v>0.4340766233817083</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.07089561223983765</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.07536333809757498</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4661353960000179</v>
+        <v>0.4340765866332166</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.08630842715501785</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4661350652635915</v>
+        <v>0.4340762558967902</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.09148886799812317</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4661355062454934</v>
+        <v>0.4340766968786922</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.09243518114089966</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4661348815211323</v>
+        <v>0.434076072154331</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.09811018407344818</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4661346977786732</v>
+        <v>0.4340758884118718</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.09532013535499573</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4661342935452631</v>
+        <v>0.4340754841784618</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.1008303463459015</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4661334483299511</v>
+        <v>0.4340746389631499</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.109406553208828</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4661334115814594</v>
+        <v>0.4340746022146582</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.1008581295609474</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4661335585754267</v>
+        <v>0.4340747492086254</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.1172305196523666</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4661334850784431</v>
+        <v>0.4340746757116418</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0610656701028347</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4661335585754267</v>
+        <v>0.4340747492086254</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.1159769892692566</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4661335953239186</v>
+        <v>0.4340747859571173</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.09049409627914429</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4661334850784431</v>
+        <v>0.4340746757116418</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0974760577082634</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.466133926060345</v>
+        <v>0.4340751166935438</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.08896861225366592</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4661338158148695</v>
+        <v>0.4340750064480682</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.07860647141933441</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4661337790663775</v>
+        <v>0.4340749696995763</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.08217732608318329</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4661337055693939</v>
+        <v>0.4340748962025927</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.08244989812374115</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4661336688209022</v>
+        <v>0.434074859454101</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.08170919120311737</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4661334483299511</v>
+        <v>0.4340746389631499</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.09512311220169067</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4661333748329675</v>
+        <v>0.4340745654661662</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.08794741332530975</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4661333013359839</v>
+        <v>0.4340744919691826</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.09113256633281708</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4661333380844758</v>
+        <v>0.4340745287176745</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.1062377467751503</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4661332278390003</v>
+        <v>0.434074418472199</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.101011261343956</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4661333380844758</v>
+        <v>0.4340745287176745</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.1201541721820831</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7308368500156143</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4661336320724103</v>
+        <v>0.434074822705609</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000008.xlsx
+++ b/out/Attention-mamba2_repeat_5_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.4433861970901489</v>
+        <v>-0.4433859586715698</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.4152671694755554</v>
+        <v>-0.4152670502662659</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.2963644862174988</v>
+        <v>-0.2963643670082092</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.08683616667985916</v>
+        <v>-0.086836077272892</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1749255657196045</v>
+        <v>-0.1749251186847687</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1567986309528351</v>
+        <v>-0.1567985117435455</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1360337436199188</v>
+        <v>-0.1360335946083069</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.1274871528148651</v>
+        <v>-0.1274870634078979</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.130988597869873</v>
+        <v>-0.1309884786605835</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.1284980177879333</v>
+        <v>-0.1284980475902557</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1290612816810608</v>
+        <v>-0.1290611326694489</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.129293292760849</v>
+        <v>-0.1292932033538818</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1268866956233978</v>
+        <v>-0.1268865466117859</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.1268230378627777</v>
+        <v>-0.1268229186534882</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.1524523496627808</v>
+        <v>-0.1524522602558136</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.1404784023761749</v>
+        <v>-0.1404782235622406</v>
       </c>
       <c r="JB17" t="n">
         <v>0.4399999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.1171558126807213</v>
+        <v>-0.1171557828783989</v>
       </c>
       <c r="JB18" t="n">
         <v>0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.1220157667994499</v>
+        <v>-0.1220156326889992</v>
       </c>
       <c r="JB19" t="n">
         <v>0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.1241465136408806</v>
+        <v>-0.1241463646292686</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1209422573447227</v>
+        <v>-0.1209421679377556</v>
       </c>
       <c r="JB21" t="n">
         <v>0.8599999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.1225302740931511</v>
+        <v>-0.1225301548838615</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.1226400211453438</v>
+        <v>-0.1226399466395378</v>
       </c>
       <c r="JB23" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.1224160864949226</v>
+        <v>-0.1224159523844719</v>
       </c>
       <c r="JB24" t="n">
         <v>0.4399999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.1284230649471283</v>
+        <v>-0.1284230053424835</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.1290839016437531</v>
+        <v>-0.1290838718414307</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.1216214224696159</v>
+        <v>-0.1216213777661324</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.16</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.1242384389042854</v>
+        <v>-0.1242383345961571</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.1230104044079781</v>
+        <v>-0.1230103000998497</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.02000000000000007</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.1250794231891632</v>
+        <v>-0.1250793039798737</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.1662095487117767</v>
+        <v>-0.1662093102931976</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.1497743725776672</v>
+        <v>-0.1497740745544434</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.1311309635639191</v>
+        <v>-0.1311308443546295</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.1289430260658264</v>
+        <v>-0.1289428770542145</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.1284578442573547</v>
+        <v>-0.12845778465271</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.16</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.1330274641513824</v>
+        <v>-0.1330274045467377</v>
       </c>
       <c r="JB37" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.1232174560427666</v>
+        <v>-0.1232173964381218</v>
       </c>
       <c r="JB38" t="n">
         <v>0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.1185659244656563</v>
+        <v>-0.1185657903552055</v>
       </c>
       <c r="JB39" t="n">
         <v>0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.1441553235054016</v>
+        <v>-0.1441552042961121</v>
       </c>
       <c r="JB40" t="n">
         <v>0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.1473041176795959</v>
+        <v>-0.1473040282726288</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.1464735567569733</v>
+        <v>-0.1464735865592957</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.1631955802440643</v>
+        <v>-0.1631954610347748</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.4399999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.02207104116678238</v>
+        <v>-0.02207102626562119</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.16</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01772525906562805</v>
+        <v>0.01772518455982208</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.001066118478775024</v>
+        <v>-0.001066051423549652</v>
       </c>
       <c r="JB46" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01077421009540558</v>
+        <v>0.01077435165643692</v>
       </c>
       <c r="JB47" t="n">
         <v>0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.0347556471824646</v>
+        <v>0.03475566953420639</v>
       </c>
       <c r="JB48" t="n">
         <v>0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.01772760599851608</v>
+        <v>0.01772763580083847</v>
       </c>
       <c r="JB49" t="n">
         <v>0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.007703468203544617</v>
+        <v>0.007703505456447601</v>
       </c>
       <c r="JB50" t="n">
         <v>0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.0006521120667457581</v>
+        <v>0.0006520673632621765</v>
       </c>
       <c r="JB51" t="n">
         <v>0.5799999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.009670324623584747</v>
+        <v>0.009670309722423553</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.02000000000000007</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.01492195948958397</v>
+        <v>0.01492204144597054</v>
       </c>
       <c r="JB53" t="n">
         <v>0.1199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.02525581791996956</v>
+        <v>0.02525575086474419</v>
       </c>
       <c r="JB54" t="n">
         <v>0.1199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.02645654603838921</v>
+        <v>0.0264565497636795</v>
       </c>
       <c r="JB55" t="n">
         <v>0.2599999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.02506007626652718</v>
+        <v>0.02506006136536598</v>
       </c>
       <c r="JB56" t="n">
         <v>0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.03204477950930595</v>
+        <v>0.03204479441046715</v>
       </c>
       <c r="JB57" t="n">
         <v>0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.07577303051948547</v>
+        <v>0.07577299326658249</v>
       </c>
       <c r="JB59" t="n">
         <v>0.8599999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.03355105593800545</v>
+        <v>0.0335509404540062</v>
       </c>
       <c r="JB60" t="n">
         <v>0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.01808534935116768</v>
+        <v>0.01808527857065201</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.02000000000000007</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.01152353733778</v>
+        <v>0.0115235224366188</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.07669391483068466</v>
+        <v>0.07669369131326675</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.16</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.1300777196884155</v>
+        <v>0.1300776600837708</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.02000000000000007</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.02609039470553398</v>
+        <v>0.02609021589159966</v>
       </c>
       <c r="JB65" t="n">
         <v>0.1199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.01889290288090706</v>
+        <v>0.01889277994632721</v>
       </c>
       <c r="JB66" t="n">
         <v>0.2599999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.06375201046466827</v>
+        <v>0.06375180929899216</v>
       </c>
       <c r="JB67" t="n">
         <v>0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.09938875585794449</v>
+        <v>0.0993887186050415</v>
       </c>
       <c r="JB68" t="n">
         <v>0.8599999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.09025605022907257</v>
+        <v>0.09025594592094421</v>
       </c>
       <c r="JB69" t="n">
         <v>0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.09857391566038132</v>
+        <v>0.09857381880283356</v>
       </c>
       <c r="JB70" t="n">
         <v>0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.09509161859750748</v>
+        <v>0.0950915589928627</v>
       </c>
       <c r="JB71" t="n">
         <v>0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.09137557446956635</v>
+        <v>0.09137552976608276</v>
       </c>
       <c r="JB72" t="n">
         <v>0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1059064492583275</v>
+        <v>0.1059063076972961</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.113601341843605</v>
+        <v>0.113601416349411</v>
       </c>
       <c r="JB74" t="n">
         <v>0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1072305291891098</v>
+        <v>0.1072306409478188</v>
       </c>
       <c r="JB75" t="n">
         <v>0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.1056734994053841</v>
+        <v>0.1056735068559647</v>
       </c>
       <c r="JB76" t="n">
         <v>0.1199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.08457488566637039</v>
+        <v>0.08457499742507935</v>
       </c>
       <c r="JB77" t="n">
         <v>0.1199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1016136109828949</v>
+        <v>0.1016136333346367</v>
       </c>
       <c r="JB78" t="n">
         <v>0.1199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1181949302554131</v>
+        <v>0.1181951612234116</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.02000000000000007</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.1238486468791962</v>
+        <v>0.1238485649228096</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.07010973989963531</v>
+        <v>0.07010968029499054</v>
       </c>
       <c r="JB81" t="n">
         <v>0.2599999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.1206477582454681</v>
+        <v>0.1206474974751472</v>
       </c>
       <c r="JB82" t="n">
         <v>0.1199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.1059547960758209</v>
+        <v>0.1059547141194344</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.1115384101867676</v>
+        <v>0.1115385666489601</v>
       </c>
       <c r="JB84" t="n">
         <v>0.1199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0800538957118988</v>
+        <v>0.08005377650260925</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.0924418643116951</v>
+        <v>0.09244193881750107</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.09762071818113327</v>
+        <v>0.09762077778577805</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.08300141245126724</v>
+        <v>-0.0830015167593956</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.01217237114906311</v>
+        <v>-0.01217225193977356</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.8599999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.06935102492570877</v>
+        <v>-0.06935099512338638</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.006741978228092194</v>
+        <v>-0.006741993129253387</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.06228351593017578</v>
+        <v>0.06228352338075638</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.08608069270849228</v>
+        <v>0.08608059585094452</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.08650723099708557</v>
+        <v>0.08650714159011841</v>
       </c>
       <c r="JB94" t="n">
         <v>0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.08639615029096603</v>
+        <v>0.08639609813690186</v>
       </c>
       <c r="JB95" t="n">
         <v>0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.09167829900979996</v>
+        <v>0.09167793393135071</v>
       </c>
       <c r="JB96" t="n">
         <v>0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.08742745220661163</v>
+        <v>0.08742757141590118</v>
       </c>
       <c r="JB97" t="n">
         <v>0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.09026491641998291</v>
+        <v>0.09026500582695007</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1050290614366531</v>
+        <v>0.105029284954071</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.04824085161089897</v>
+        <v>0.04824082925915718</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.0100543275475502</v>
+        <v>-0.01005447655916214</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.07089561223983765</v>
+        <v>0.07089543342590332</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.08630842715501785</v>
+        <v>0.08630827814340591</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.09148886799812317</v>
+        <v>0.09148889780044556</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.02000000000000007</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.09243518114089966</v>
+        <v>0.09243495762348175</v>
       </c>
       <c r="JB105" t="n">
         <v>0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.09811018407344818</v>
+        <v>0.09811022877693176</v>
       </c>
       <c r="JB106" t="n">
         <v>0.8599999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.09532013535499573</v>
+        <v>0.09532008320093155</v>
       </c>
       <c r="JB107" t="n">
         <v>0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.1008303463459015</v>
+        <v>0.1008301824331284</v>
       </c>
       <c r="JB108" t="n">
         <v>0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.109406553208828</v>
+        <v>0.1094063073396683</v>
       </c>
       <c r="JB109" t="n">
         <v>0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.1008581295609474</v>
+        <v>0.1008580178022385</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.1172305196523666</v>
+        <v>0.117230586707592</v>
       </c>
       <c r="JB111" t="n">
         <v>0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0610656701028347</v>
+        <v>0.06106558069586754</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.02000000000000007</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.1159769892692566</v>
+        <v>0.1159770414233208</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.09049409627914429</v>
+        <v>0.0904940590262413</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.0974760577082634</v>
+        <v>0.0974760502576828</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.02000000000000007</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.08896861225366592</v>
+        <v>0.08896872401237488</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.07860647141933441</v>
+        <v>0.07860638201236725</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.08217732608318329</v>
+        <v>0.08217743039131165</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.16</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.08244989812374115</v>
+        <v>0.08245003223419189</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.08170919120311737</v>
+        <v>0.08170922100543976</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.16</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.09512311220169067</v>
+        <v>0.09512366354465485</v>
       </c>
       <c r="JB121" t="n">
         <v>0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.08794741332530975</v>
+        <v>0.08794743567705154</v>
       </c>
       <c r="JB122" t="n">
         <v>0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.09113256633281708</v>
+        <v>0.09113260358572006</v>
       </c>
       <c r="JB123" t="n">
         <v>0.7199999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.1062377467751503</v>
+        <v>0.1062378734350204</v>
       </c>
       <c r="JB124" t="n">
         <v>0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.101011261343956</v>
+        <v>0.1010111942887306</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9299999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.1201541721820831</v>
+        <v>0.1201540678739548</v>
       </c>
       <c r="JB126" t="n">
         <v>1.14</v>
